--- a/VAPs APIs.xlsx
+++ b/VAPs APIs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammad\Downloads\Postman Collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malhaddad\Downloads\SQL-Project-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9FBE919-30AF-4529-BC0E-8F4A0A6DE5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{204E33C5-4E3C-40EE-91EC-106CD2AED999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BA354C8C-BCC9-4E42-A8B0-C30273EA75BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA354C8C-BCC9-4E42-A8B0-C30273EA75BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>IBAN Verification</t>
   </si>
@@ -234,12 +234,43 @@
   <si>
     <t>https://test.api.neotek.sa/salary-certificate-lite/v1/persons/1186897433?POIType=NAT&amp;EmploymentSector=Gov&amp;BirthDate=1989-08-12&amp;BirthDateType=Greg</t>
   </si>
+  <si>
+    <t>Get Establishment Employees Details List
+Get Establishment Employment Information
+Get Person Employment Information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get Government Employment Details
+Get Government Employment Info
+</t>
+  </si>
+  <si>
+    <t>https://test.api.neotek.sa/government-employment-info/v1/persons/1123456789?POIType=NAT&amp;BirthDate=1989-08-12&amp;BirthDateType=Greg
+https://test.api.neotek.sa/government-employment-details/v1/persons/1123456789?POIType=NAT&amp;BirthDate=1989-08-12&amp;BirthDateType=Greg&amp;PayMonth=2022-09&amp;PayMonthType=Greg</t>
+  </si>
+  <si>
+    <t>https://test.api.neotek.sa/employment-info/v1/persons/1123456789
+https://test.api.neotek.sa/employment-info/v1/establishments/1
+https://test.api.neotek.sa/employment-info/v1/establishments/1/employees</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>List of APIs</t>
+  </si>
+  <si>
+    <t>APIs Count</t>
+  </si>
+  <si>
+    <t>APIs URLs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,6 +282,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -271,17 +309,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -292,27 +358,29 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -332,9 +400,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -372,7 +440,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -478,7 +546,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -620,7 +688,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -628,336 +696,364 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9561742-5DE3-4FFB-B4EE-457903B16FC5}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="58.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="115" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="58.42578125" style="1"/>
+    <col min="5" max="5" width="115" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E12" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E13" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E14" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="C16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="1" t="s">
+    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E13" r:id="rId1" xr:uid="{0318B1B0-E5B9-43A0-B0F2-C4D8F1798F7D}"/>
-    <hyperlink ref="E12" r:id="rId2" xr:uid="{B1E7BE45-92EE-4834-A1D2-626D3A84AE1F}"/>
-    <hyperlink ref="E11" r:id="rId3" xr:uid="{5707215F-1E12-48EC-8094-848D49259F99}"/>
+    <hyperlink ref="E14" r:id="rId1" xr:uid="{0318B1B0-E5B9-43A0-B0F2-C4D8F1798F7D}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{B1E7BE45-92EE-4834-A1D2-626D3A84AE1F}"/>
+    <hyperlink ref="E12" r:id="rId3" xr:uid="{5707215F-1E12-48EC-8094-848D49259F99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K008000 Ejada Public Information</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b5ab016a-022d-4842-b407-a61897a39a0c}" enabled="1" method="Privileged" siteId="{e1304ad9-93ba-4557-8b20-8c1c1143b399}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>